--- a/02_加值成品/八下/八下5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-3 有機物與生活　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下5-3 有機物與生活　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>質輕耐用但難分解的聚合物？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>塑膠</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>減塑</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>聚合物</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>親油端</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>常見</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>清潔劑分子一端親水一端？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>親油</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>質輕耐用可塑</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>油污</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>塑膠</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>兩性</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>清潔劑如何去油污？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>包住油污隨水沖走</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>減少一次性塑膠</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>危害生物與人體健康</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>來源不同皆為聚合物</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>塑膠難分解會造成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>資源回收</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>減塑</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>回收分類</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>環境污染</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>課題</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>尼龍聚酯屬於？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>合成纖維</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>質輕耐用可塑</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>親油</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>環境污染</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>聚合物</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>寶特瓶應如何處理？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>聚合物</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>親油</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>回收分類</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>合成纖維</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>再利用</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>減少塑膠使用稱？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>減塑</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>環境污染</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>親油</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>質輕耐用可塑</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>環保</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>橡膠具有什麼特性？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>彈性</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>質輕耐用可塑</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>環境污染</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>塑膠</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>聚合物</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>清潔劑能去油因分子有親水與？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>塑膠</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>油污</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>減塑</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>親油端</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>兩性</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>回收寶特瓶屬於哪種環保行動？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>質輕耐用可塑</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>資源回收</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>親油</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>合成纖維</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>回收</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-3 有機物與生活　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下5-3 有機物與生活　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>洗碗精能去油因分子有？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>聚合物穩定不易被分解累積</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>相似(親油親水)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>減少污染兼顧便利</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>親油端與親水端</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>結構</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>塑膠依標示分類是為了？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>彈性</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>親油</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>正確回收</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>資源回收</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>再利用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>微塑膠問題來自？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>塑膠碎裂難分解</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>親油端插入油污、親水端朝外,形成微胞隨水帶走</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>親油端包油親水端向外隨水沖走</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>塑膠難分解造成污染</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>污染</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>合成纖維與天然纖維都是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>減塑</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>親油</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>合成纖維</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>聚合物</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>高分子</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>肥皂去污與清潔劑原理？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>塑膠碎裂難分解</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>相似(親油親水)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>正確處理再利用</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>材質不同需分開處理再製</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>兩性</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>塑膠優點包括？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>質輕耐用可塑</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>資源回收</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>回收分類</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>塑膠</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>環保購物袋目的？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>減少一次性塑膠</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>減少污染兼顧便利</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>塑膠難分解造成污染</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>聚合物穩定不易被分解累積</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>減塑</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>清潔劑親油端朝向？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>油污</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>回收分類</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>親油</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>塑膠</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>包覆</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>塑膠標示分類回收是為了？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>包住油污隨水沖走</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>正確處理再利用</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>減少污染兼顧便利</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>親油端包油親水端向外隨水沖走</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>回收</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>尼龍屬於天然還合成纖維？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>聚合物</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>回收分類</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>合成纖維</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>環境污染</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>人造</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-3 有機物與生活　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下5-3 有機物與生活　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>用分子結構解釋清潔劑去油全過程？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>減少一次性塑膠</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>塑膠難分解造成污染</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>來源不同皆為聚合物</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>親油端插入油污、親水端朝外,形成微胞隨水帶走</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>塑膠難分解為何造成長期污染？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>聚合物穩定不易被分解累積</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>親油端與親水端</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相似(親油親水)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>減少污染兼顧便利</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>環境</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>如何從生活減少塑膠污染？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>相似(親油親水)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>減少一次性塑膠</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>材質不同需分開處理再製</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>減量重複使用回收替代</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>方案</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>為何塑膠要分類回收？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>塑膠難分解造成污染</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>正確處理再利用</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>材質不同需分開處理再製</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>減少污染兼顧便利</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>回收</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>微塑膠可能進入食物鏈影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>危害生物與人體健康</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>減少污染兼顧便利</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>相似(親油親水)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>正確處理再利用</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>風險</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>比較天然橡膠與合成橡膠？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>包住油污隨水沖走</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>正確處理再利用</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>來源不同皆為聚合物</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>親油端插入油污、親水端朝外,形成微胞隨水帶走</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>清潔劑排入河川可能造成？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>減少一次性塑膠</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>親油端與親水端</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>水質污染影響生態</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>親油端包油親水端向外隨水沖走</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>研發可分解塑膠的意義？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>危害生物與人體健康</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>減少污染兼顧便利</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>水質污染影響生態</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>減量重複使用回收替代</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>永續</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>清潔劑分子如何把油污帶走？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>親油端與親水端</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>親油端包油親水端向外隨水沖走</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>包住油污隨水沖走</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>親油端插入油污、親水端朝外,形成微胞隨水帶走</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何提倡減少一次性塑膠？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>包住油污隨水沖走</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>減少一次性塑膠</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>塑膠碎裂難分解</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>塑膠難分解造成污染</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>減塑</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>常見</t>
+          <t>常見：塑膠又輕又耐用，生活中隨處可見，但它的分子結構穩定，很難被自然分解掉</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>兩性</t>
+          <t>兩性：清潔劑的分子一頭喜歡靠近水，另一頭喜歡靠近油，具有兩種相反的性質</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：清潔劑分子的親油端會鑽進油污裡，親水端朝外，把整個油污包裹起來隨水沖走</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>課題</t>
+          <t>課題：塑膠丟棄後長時間留在環境中不會消失，累積越來越多就形成了環境污染的問題</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>聚合物</t>
+          <t>聚合物：尼龍和聚酯都是人工合成出來、由小分子連接而成的纖維，屬於有機聚合物</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>再利用</t>
+          <t>再利用：寶特瓶用完後應該依照標示分類回收，才能被重新處理製成新的產品</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>環保</t>
+          <t>環保：主動減少使用塑膠製品、改用可重複利用的物品，這樣的行動就叫做減塑</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>聚合物</t>
+          <t>聚合物：橡膠這種聚合物的分子結構能被拉伸又能彈回原狀，具有很好的彈性</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>兩性</t>
+          <t>兩性：清潔劑分子一端親水、另一端親油，這種兩性的構造使它能同時和油污與水結合，幫助把油污帶離物體表面</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>回收</t>
+          <t>回收：把用過的寶特瓶收集起來，經過處理後重新製成新產品再利用，屬於資源回收的環保行動</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>結構</t>
+          <t>結構：洗碗精分子同時擁有親油和親水兩端，讓它能同時抓住油污又能被水沖走</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>再利用</t>
+          <t>再利用：不同材質的塑膠處理方式不同，依照標示分類才能讓回收廠正確處理再製成新產品</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>污染：大塊塑膠在環境中經過風化，慢慢碎裂成極小的微塑膠顆粒，卻依然難以分解消失</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>高分子</t>
+          <t>高分子：不管是人工合成的還是自然界原有的，纖維都是由小分子重複連接組成的巨大分子</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>兩性</t>
+          <t>兩性：肥皂分子也和清潔劑一樣，一端親油一端親水，靠這個結構把油污帶走</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>特性：塑膠重量輕、使用壽命長，還能被塑造成各種形狀，這些都是它被廣泛使用的優點</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>減塑</t>
+          <t>減塑：使用能重複利用的環保購物袋，可以減少一次性塑膠袋的消耗，達到環保的目的</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>包覆</t>
+          <t>包覆：清潔劑分子的親油端會主動朝向油污的方向靠近，把它包裹住方便帶走</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>回收</t>
+          <t>回收：不同種類的塑膠材質與熔點不同，標示分類可以讓回收處理時依照材質正確分開處理，提高再利用的效率與品質</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>人造</t>
+          <t>人造：尼龍是由人工合成的聚合物纖維，不是自然界天然生成的纖維，屬於合成纖維</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：清潔劑的親油端鑽進油污內部，親水端則朝外露出，把油污包成一個小球狀，隨著水流一起沖走</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>環境</t>
+          <t>環境：塑膠的分子連接非常穩固，微生物幾乎無法分解它，一旦丟棄就會長期留在環境中不斷累積</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>方案</t>
+          <t>方案：可以從減少使用、重複利用、確實回收，以及改用其他材質替代這幾個方向著手減少污染</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>回收</t>
+          <t>回收：不同種類的塑膠熔點和特性都不一樣，必須分開處理才能順利再製成新的塑膠產品</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>風險</t>
+          <t>風險：微小的塑膠顆粒可能被魚類等生物誤食，經由食物鏈一層層累積，最終可能危害到人體健康</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：天然橡膠是從橡膠樹採集提煉出來的，合成橡膠是人工化學合成的，但兩者本質上都是聚合物</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>環境</t>
+          <t>環境：清潔劑若大量流入河川，會改變水質、影響水中生物的生存，破壞河川的生態環境</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>永續</t>
+          <t>永續：可分解塑膠能在自然環境中較快被分解掉，讓人們還能享受塑膠的便利，同時減少對環境的傷害</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：清潔劑分子的親油端會鑽入並包覆住油污，親水端則朝外和水接觸，形成一顆顆小顆粒懸浮在水中，最後隨著清水沖洗被帶走</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>減塑</t>
+          <t>減塑：塑膠在自然環境中很難被分解，長期累積會造成土壤、海洋等環境污染，甚至危害野生動物，所以提倡減少使用一次性塑膠製品</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下5-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-3_三種難度測驗卷.xlsx
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>質輕耐用可塑</t>
+          <t>環境污染</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>油污</t>
+          <t>彈性</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>塑膠</t>
+          <t>減塑</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>油污</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>聚合物</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>塑膠</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>油污</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>減塑</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
